--- a/InputData/cpi.xlsx
+++ b/InputData/cpi.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{698147E0-8145-46CB-AA60-1ED82BEC5780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21B39BD3-42AA-4DDE-BCD1-0F086876A133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="78">
   <si>
     <t>CPI Consumer Price Index</t>
   </si>
@@ -262,6 +262,9 @@
   </si>
   <si>
     <t>https://data.bls.gov/pdq/SurveyOutputServlet</t>
+  </si>
+  <si>
+    <t>2024............................................................................. .</t>
   </si>
 </sst>
 </file>
@@ -2098,7 +2101,22 @@
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="G62" s="6"/>
+      <c r="A62" t="s">
+        <v>77</v>
+      </c>
+      <c r="B62">
+        <v>312.14499999999998</v>
+      </c>
+      <c r="C62">
+        <v>315.233</v>
+      </c>
+      <c r="D62">
+        <v>313.68900000000002</v>
+      </c>
+      <c r="G62" s="6">
+        <f>$D$50/D62</f>
+        <v>0.73191600598044548</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
